--- a/src/test_data/data.xlsx
+++ b/src/test_data/data.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\VSCODE\Playwright_Automation_TS\DemoQA\src\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751B2F10-31A0-4243-A84A-BED4761BF5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5851BCCA-008B-4D92-9769-95FC68CB495C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1120CC49-D95F-4BF2-BC9C-D733C0CBC652}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>TestScriptName</t>
   </si>
@@ -39,19 +39,40 @@
     <t>pURL</t>
   </si>
   <si>
-    <t>pUserName</t>
-  </si>
-  <si>
-    <t>pPassword</t>
-  </si>
-  <si>
     <t>chrome</t>
   </si>
   <si>
-    <t>Login to DemoQA website</t>
-  </si>
-  <si>
     <t>https://demoqa.com/</t>
+  </si>
+  <si>
+    <t>pFullName</t>
+  </si>
+  <si>
+    <t>pEmailID</t>
+  </si>
+  <si>
+    <t>pCurrentAddress</t>
+  </si>
+  <si>
+    <t>pPermanentAddress</t>
+  </si>
+  <si>
+    <t>Sathya Mohan</t>
+  </si>
+  <si>
+    <t>sathya.mohan181986@gmail.com</t>
+  </si>
+  <si>
+    <t>Saravanampatti</t>
+  </si>
+  <si>
+    <t>TC1 - Login &amp; Text Box elts with valid input</t>
+  </si>
+  <si>
+    <t>TC1 - Login &amp; Text Box elts with invalid input</t>
+  </si>
+  <si>
+    <t>sathya.mohan181986</t>
   </si>
 </sst>
 </file>
@@ -414,17 +435,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{726F6662-5AB1-4B30-B11F-301067991C44}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -438,29 +461,76 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{86468A09-B8DB-4889-9DE2-5470CD5DA9A2}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{FCB66C38-3C7B-4C2E-A610-3FA7D6CAC632}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{11E30479-2DEA-430D-A366-3ED97383F0D7}"/>
+    <hyperlink ref="F3" r:id="rId4" display="sathya.mohan181986@gmail.com" xr:uid="{21924FE4-D993-410A-85EF-EBE114F4B139}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
